--- a/netflix_tv_shows.xlsx
+++ b/netflix_tv_shows.xlsx
@@ -9440,10 +9440,10 @@
         <v>32.565</v>
       </c>
       <c r="F265" t="n">
-        <v>7.3</v>
+        <v>7.5</v>
       </c>
       <c r="G265" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="H265" t="inlineStr">
         <is>
@@ -10834,10 +10834,10 @@
         <v>30.0429</v>
       </c>
       <c r="F306" t="n">
-        <v>7.229</v>
+        <v>7.232</v>
       </c>
       <c r="G306" t="n">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="H306" t="inlineStr">
         <is>
@@ -10973,7 +10973,7 @@
         <v>8.696</v>
       </c>
       <c r="G310" t="n">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="H310" t="inlineStr">
         <is>
@@ -11038,10 +11038,10 @@
         <v>29.4938</v>
       </c>
       <c r="F312" t="n">
-        <v>7.697</v>
+        <v>7.705</v>
       </c>
       <c r="G312" t="n">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="H312" t="inlineStr">
         <is>
@@ -11140,7 +11140,7 @@
         <v>29.4292</v>
       </c>
       <c r="F315" t="n">
-        <v>6.667</v>
+        <v>6.7</v>
       </c>
       <c r="G315" t="n">
         <v>456</v>
